--- a/ratings_missing_years.xlsx
+++ b/ratings_missing_years.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="8">
   <si>
     <t>Code</t>
   </si>
@@ -28,19 +28,10 @@
     <t>EGY</t>
   </si>
   <si>
-    <t>FRA</t>
-  </si>
-  <si>
     <t>GRC</t>
   </si>
   <si>
     <t>JPN</t>
-  </si>
-  <si>
-    <t>UK</t>
-  </si>
-  <si>
-    <t>USA</t>
   </si>
   <si>
     <t>VNM</t>
@@ -404,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -460,60 +451,60 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>2001</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8">
-        <v>2002</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9">
-        <v>2003</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10">
-        <v>2004</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B11">
-        <v>2006</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B12">
-        <v>2007</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B13">
-        <v>2008</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B14">
         <v>2009</v>
@@ -521,233 +512,33 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B15">
-        <v>2010</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B16">
-        <v>2006</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B17">
-        <v>2003</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>7</v>
-      </c>
-      <c r="B25">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>9</v>
-      </c>
-      <c r="B39">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>9</v>
-      </c>
-      <c r="B40">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>10</v>
-      </c>
-      <c r="B42">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>10</v>
-      </c>
-      <c r="B43">
         <v>2010</v>
       </c>
     </row>

--- a/ratings_missing_years.xlsx
+++ b/ratings_missing_years.xlsx
@@ -14,15 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
   <si>
     <t>Code</t>
   </si>
   <si>
     <t>Year_missing</t>
-  </si>
-  <si>
-    <t>ARG</t>
   </si>
   <si>
     <t>EGY</t>
@@ -395,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -411,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>2002</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -419,31 +416,31 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2004</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
-        <v>2023</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>2006</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6">
-        <v>2010</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -451,7 +448,7 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>2006</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -459,7 +456,7 @@
         <v>5</v>
       </c>
       <c r="B8">
-        <v>2003</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -467,7 +464,7 @@
         <v>5</v>
       </c>
       <c r="B9">
-        <v>2008</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -475,31 +472,31 @@
         <v>5</v>
       </c>
       <c r="B10">
-        <v>2009</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11">
-        <v>2000</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B12">
-        <v>2003</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13">
-        <v>2004</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -507,7 +504,7 @@
         <v>6</v>
       </c>
       <c r="B14">
-        <v>2009</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -515,30 +512,6 @@
         <v>6</v>
       </c>
       <c r="B15">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18">
         <v>2010</v>
       </c>
     </row>
